--- a/System_development/Van-Hove/PCB_design/NMR Control Board v0.4.5/PCB_Control_Board_V_0.4.5_BoM.xlsx
+++ b/System_development/Van-Hove/PCB_design/NMR Control Board v0.4.5/PCB_Control_Board_V_0.4.5_BoM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Compact-NMR\System_development\Van-Hove\PCB_design\NMR Control Board V 0.4.4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jimmy\OneDrive\Documents\GitHub\Compact-NMR\System_development\Van-Hove\PCB_design\NMR Control Board v0.4.5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A66B56C-93A3-4EF2-9D6A-FD753AF5374A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38229ED6-EC72-499E-A2FA-0EFEC4653A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="119">
   <si>
     <t>Total Cost</t>
   </si>
@@ -101,15 +101,9 @@
     <t>NCP715sQ18T2G</t>
   </si>
   <si>
-    <t xml:space="preserve">Capacitors </t>
-  </si>
-  <si>
     <t>0.1 uF Capacitors</t>
   </si>
   <si>
-    <t>1 nf Capacitors</t>
-  </si>
-  <si>
     <t>0.33 uf Capacitors</t>
   </si>
   <si>
@@ -143,12 +137,6 @@
     <t>BAT6404E6433HTMA1</t>
   </si>
   <si>
-    <t>Female Board Edge SMA Connector</t>
-  </si>
-  <si>
-    <t>CON-SMA-EDGE-S</t>
-  </si>
-  <si>
     <t>Female Through Hole SMA Connector</t>
   </si>
   <si>
@@ -191,9 +179,6 @@
     <t>https://www.digikey.com/en/products/detail/adam-tech/RF2-04A-T-00-50-G/9830588</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/rf-solutions/CON-SMA-EDGE-S/5845767</t>
-  </si>
-  <si>
     <t>https://www.digikey.com/en/products/detail/infineon-technologies/BAT6404E6433HTMA1/1280948?s=N4IgTCBcDaIEIEEAqA2ALABjQUXQZjwAkkBZBARhAF0BfIA</t>
   </si>
   <si>
@@ -260,9 +245,6 @@
     <t>https://www.mouser.com/ProductDetail/Infineon-Technologies/BAT6404E6433HTMA1?qs=K00xGehIlju31KA4KMtgCQ%3D%3D</t>
   </si>
   <si>
-    <t>https://www.mouser.com/ProductDetail/RF-Solutions/CON-SMA-EDGE-S?qs=UkDUCjYnTB3a941HfsgOOA%3D%3D</t>
-  </si>
-  <si>
     <t>https://www.mouser.com/ProductDetail/Adam-Tech/RF2-04A-T-00-50-G?qs=HoCaDK9Nz5dc3qwWN4DjGA%3D%3D</t>
   </si>
   <si>
@@ -311,10 +293,106 @@
     <t>https://www.newark.com/infineon/bat6404e6433htma1/diode-schottky-aec-q101-40v-sot23/dp/68AC4382</t>
   </si>
   <si>
-    <t>https://sa.rsdelivers.com/product/rf-solutions/con-sma-edge-s/rf-solutions-con-series-jack-sma-connector-solder/1258191?srsltid=AfmBOorKtUPg18WFoD31Vi2GhuiHceVmlkenSwGlArAdXQb6uUC_Ka5t</t>
-  </si>
-  <si>
     <t>https://www.heilind.com/adtrf2-04a-t-00-50-g.html?&amp;utm_source=octopart&amp;utm_medium=buy</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>U5</t>
+  </si>
+  <si>
+    <t>Power_Splitter</t>
+  </si>
+  <si>
+    <t>Mixer_Mixer</t>
+  </si>
+  <si>
+    <t>U6</t>
+  </si>
+  <si>
+    <t>U4</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>1 uF Capacitors</t>
+  </si>
+  <si>
+    <t>1 nF Capacitors</t>
+  </si>
+  <si>
+    <t>C4, C8, C9</t>
+  </si>
+  <si>
+    <t>C1, C2, C3, C15</t>
+  </si>
+  <si>
+    <t>C10, C11, C12</t>
+  </si>
+  <si>
+    <t>C13, C14</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>D8, D9, D10</t>
+  </si>
+  <si>
+    <t>D1, D2, D3, D4</t>
+  </si>
+  <si>
+    <t>J1-J12</t>
+  </si>
+  <si>
+    <t>Vendor 4</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.us/item/3256804056009500.html?spm=a2g0o.productlist.main.2.30276febieJcvn&amp;algo_pvid=909743e4-35c2-4e86-8d65-7d8d115ba05f&amp;algo_exp_id=909743e4-35c2-4e86-8d65-7d8d115ba05f-1&amp;pdp_ext_f=%7B%22order%22%3A%226336%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21USD%212.60%210.99%21%21%212.60%210.99%21%4021030a4b17757515549945973e60dd%2112000056072044332%21sea%21US%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3A1ebdde83%3Bm03_new_user%3A-29895%3BpisId%3A5000000197847434&amp;curPageLogUid=FLqHVcrTDnmC&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005004242324252%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/kyocera-avx/06035A620JAT2A/1599919</t>
+  </si>
+  <si>
+    <t>68 pF Capacitor</t>
+  </si>
+  <si>
+    <t>68 pF ±5% 50V Ceramic Capacitor C0G, NP0 0402 (1005 Metric)</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/samsung-electro-mechanics/CL05C680JB51PNC/5961075</t>
+  </si>
+  <si>
+    <t>https://www.mouser.com/ProductDetail/Samsung-Electro-Mechanics/CL05C680JB51PNC?qs=Qj6zq1TuXccLoUfUcVMRpg%3D%3D&amp;srsltid=AfmBOoqEiTbEeK390TP7trsii-YceePAIfLmiKYXj3QOj_dN5XZNFEpd</t>
+  </si>
+  <si>
+    <t>https://www.tme.com/in/en/details/cl05c680jb51pnc/mlcc-smd-capacitors/samsung/</t>
+  </si>
+  <si>
+    <t>62 pF Capacitor</t>
+  </si>
+  <si>
+    <t>https://www.mouser.com/ProductDetail/KYOCERA-AVX/06035A620JAT2A?qs=VYVmvnYLdvmMNkKlwnY2DA%3D%3D&amp;srsltid=AfmBOopgsyC5QFua0Po9VQiPl_nxzOGa_XvbMg2lB5IDWXMeV3X7dhGE</t>
+  </si>
+  <si>
+    <t>https://www.newark.com/kyocera-avx/06035a620jat2a/capacitor-62pf-c0g-np0-50v-0603/dp/41AM3452</t>
+  </si>
+  <si>
+    <t>62 pF ±5% 50V Ceramic Capacitor C0G, NP0 0603 (1608 Metric)</t>
   </si>
 </sst>
 </file>
@@ -324,7 +402,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -344,6 +422,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -370,25 +454,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="7">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -404,17 +508,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{77BB0EBA-7ABD-4504-8B56-065735F83FAF}" name="Table1" displayName="Table1" ref="A1:H18" totalsRowShown="0" dataCellStyle="Hyperlink">
-  <autoFilter ref="A1:H18" xr:uid="{77BB0EBA-7ABD-4504-8B56-065735F83FAF}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{125445A2-3E64-47DE-B26B-B36D09088CF3}" name="Designator"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{77BB0EBA-7ABD-4504-8B56-065735F83FAF}" name="Table1" displayName="Table1" ref="A1:J19" totalsRowShown="0" dataCellStyle="Hyperlink">
+  <autoFilter ref="A1:J19" xr:uid="{77BB0EBA-7ABD-4504-8B56-065735F83FAF}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{125445A2-3E64-47DE-B26B-B36D09088CF3}" name="Designator" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{216FE132-2E18-40F7-A20A-BBFD26EC9D9D}" name="Reference"/>
     <tableColumn id="2" xr3:uid="{978F1655-82E8-4669-A0DF-8FC026E7C5CF}" name="Component"/>
     <tableColumn id="3" xr3:uid="{B31F8100-EC13-4F33-9A36-9A86A9F32309}" name="Amount"/>
-    <tableColumn id="4" xr3:uid="{B43A5C30-725D-41B9-ADE9-63C238F6193D}" name="Individual Cost" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{D2C286B4-CC55-46B0-8AA4-9B8C5B8E8252}" name="Total Cost" dataDxfId="0"/>
-    <tableColumn id="6" xr3:uid="{05D9E9D4-6FDB-4462-ABB6-67CC55FED516}" name="Vendor 1" dataCellStyle="Hyperlink"/>
-    <tableColumn id="7" xr3:uid="{1351036D-0F08-4053-99CA-5A59FD8F86C2}" name="Vendor 2" dataCellStyle="Hyperlink"/>
-    <tableColumn id="8" xr3:uid="{A6791673-9B53-4B1D-9E7C-56277BA3A1DB}" name="Vendor 3" dataCellStyle="Hyperlink"/>
+    <tableColumn id="4" xr3:uid="{B43A5C30-725D-41B9-ADE9-63C238F6193D}" name="Individual Cost" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{D2C286B4-CC55-46B0-8AA4-9B8C5B8E8252}" name="Total Cost" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{05D9E9D4-6FDB-4462-ABB6-67CC55FED516}" name="Vendor 1" dataDxfId="3" dataCellStyle="Hyperlink"/>
+    <tableColumn id="7" xr3:uid="{1351036D-0F08-4053-99CA-5A59FD8F86C2}" name="Vendor 2" dataDxfId="2" dataCellStyle="Hyperlink"/>
+    <tableColumn id="8" xr3:uid="{A6791673-9B53-4B1D-9E7C-56277BA3A1DB}" name="Vendor 3" dataDxfId="1" dataCellStyle="Hyperlink"/>
+    <tableColumn id="10" xr3:uid="{071AC535-6AD2-4958-86AD-B45E57B01236}" name="Vendor 4" dataDxfId="0" dataCellStyle="Hyperlink"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -737,554 +843,661 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:H19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="74" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" customWidth="1"/>
-    <col min="5" max="5" width="23.5703125" customWidth="1"/>
-    <col min="6" max="6" width="41.28515625" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="74" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="23.88671875" customWidth="1"/>
+    <col min="6" max="6" width="23.5546875" customWidth="1"/>
+    <col min="7" max="7" width="41.33203125" customWidth="1"/>
+    <col min="8" max="8" width="18.5546875" customWidth="1"/>
+    <col min="9" max="9" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>0</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.52</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.52</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="5"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.77</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.77</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J3" s="5"/>
+    </row>
+    <row r="4" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1.25</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1.25</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J4" s="5"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>11.55</v>
+      </c>
+      <c r="F5" s="1">
+        <v>11.55</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J5" s="5"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>10.8</v>
+      </c>
+      <c r="F6" s="1">
+        <v>10.8</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>4.03</v>
+      </c>
+      <c r="F7" s="1">
+        <v>4.03</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="J7" s="5"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.61</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.61</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="J9" s="5"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.39</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J10" s="5"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="J11" s="5"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0.38</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="J12" s="5"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0.76</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1.38</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0.52</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0.52</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0.77</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0.77</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1.25</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1.25</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="H18" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19">
         <v>12</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2">
-        <v>11.55</v>
-      </c>
-      <c r="E5" s="2">
-        <v>11.55</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2">
-        <v>10.8</v>
-      </c>
-      <c r="E6" s="2">
-        <v>10.8</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2">
-        <v>4.03</v>
-      </c>
-      <c r="E7" s="2">
-        <v>4.03</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0.61</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0.61</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="F9" s="1" t="s">
+      <c r="E19" s="1">
+        <v>1.84</v>
+      </c>
+      <c r="F19" s="1">
+        <v>22.08</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0.39</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0.11</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0.33</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H11" s="1" t="s">
+      <c r="H19" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I19" s="5" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0.19</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0.38</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0.18</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0.18</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14">
-        <v>4</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0.19</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0.76</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15">
-        <v>4</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16">
-        <v>3</v>
-      </c>
-      <c r="D16" s="2">
-        <v>0.46</v>
-      </c>
-      <c r="E16" s="2">
-        <v>1.38</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17">
-        <v>7</v>
-      </c>
-      <c r="D17" s="2">
-        <v>1.69</v>
-      </c>
-      <c r="E17" s="2">
-        <v>10.14</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18">
-        <v>6</v>
-      </c>
-      <c r="D18" s="2">
-        <v>1.84</v>
-      </c>
-      <c r="E18" s="2">
-        <v>11.04</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D19" s="3" t="s">
+      <c r="J19" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E20" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E19" s="4">
-        <f>SUM(E2:E18)</f>
-        <v>54.78</v>
+      <c r="F20" s="3">
+        <f>SUM(F2:F19)</f>
+        <v>55.88</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{519CECF9-06B6-4E70-862E-6CF7F786775B}"/>
-    <hyperlink ref="F3" r:id="rId2" xr:uid="{C598BACE-CE8B-49FD-881F-AD2471656F65}"/>
-    <hyperlink ref="F4" r:id="rId3" xr:uid="{35C0BA64-C19E-484B-972E-D4843344E2B5}"/>
-    <hyperlink ref="F5" r:id="rId4" xr:uid="{02073409-00C2-4C51-83EC-97A07CDF9BAB}"/>
-    <hyperlink ref="F6" r:id="rId5" xr:uid="{CEEC7E8B-5F64-4DDD-BB5E-8202CED76FE4}"/>
-    <hyperlink ref="F7" r:id="rId6" xr:uid="{58EB83B7-5748-4AFA-9A18-DC92D6A5C3A5}"/>
-    <hyperlink ref="F8" r:id="rId7" xr:uid="{63324E66-EECF-420A-939D-9FC410ECA74B}"/>
-    <hyperlink ref="F9" r:id="rId8" xr:uid="{54F3D8AB-A6FA-4E4F-86DB-421A97E77B63}"/>
-    <hyperlink ref="F18" r:id="rId9" xr:uid="{A3BA962D-F109-4E59-B8E9-240AF405D6C7}"/>
-    <hyperlink ref="F17" r:id="rId10" xr:uid="{218AF3FE-0BD0-4048-A3E1-159D9AAE0B3C}"/>
-    <hyperlink ref="F16" r:id="rId11" xr:uid="{0BFA9F3D-5219-4B8C-B846-B76FFD0BF1F0}"/>
-    <hyperlink ref="F15" r:id="rId12" xr:uid="{2B6DAD25-A022-47B4-97A4-D1F53A16C922}"/>
-    <hyperlink ref="F14" r:id="rId13" xr:uid="{E67D244A-F5D5-478D-A098-E4333EDFDF4B}"/>
-    <hyperlink ref="F13" r:id="rId14" xr:uid="{5705BC2E-3933-42BB-9D8D-A4561DE31E87}"/>
-    <hyperlink ref="F12" r:id="rId15" xr:uid="{09FEC92A-8E57-4745-B2B1-CB173FE342AF}"/>
-    <hyperlink ref="F11" r:id="rId16" xr:uid="{D85B8645-75F4-4DBE-96B6-5E264C73B64D}"/>
-    <hyperlink ref="F10" r:id="rId17" xr:uid="{B42BB367-E930-4F01-8984-E1B2FFC1315A}"/>
-    <hyperlink ref="G2" r:id="rId18" xr:uid="{AC63E67E-A0B3-4A54-B1EA-D69352B35E07}"/>
-    <hyperlink ref="G3" r:id="rId19" xr:uid="{28025270-E5D5-4156-B3FB-9CAB7029620E}"/>
-    <hyperlink ref="G4" r:id="rId20" xr:uid="{7BF3CEDE-E935-45C4-AB8D-C785568BAD81}"/>
-    <hyperlink ref="G5" r:id="rId21" xr:uid="{3ECF6EA4-A634-4F9B-B1AB-0A182259698F}"/>
-    <hyperlink ref="G6" r:id="rId22" xr:uid="{7412DBB7-8AF9-4525-B14C-686F7197DFE7}"/>
-    <hyperlink ref="G7" r:id="rId23" xr:uid="{F9D5EEB3-CFF4-4E31-B844-D1A3572D9FA9}"/>
-    <hyperlink ref="G8" r:id="rId24" xr:uid="{63C8E88F-8E99-4823-B700-9B5B55D315CF}"/>
-    <hyperlink ref="G9" r:id="rId25" xr:uid="{C8D10D9F-D84E-41EB-AA2A-0C871FD32342}"/>
-    <hyperlink ref="G10" r:id="rId26" xr:uid="{85687F6A-272F-45B5-8586-33E1B62F6EB3}"/>
-    <hyperlink ref="G11" r:id="rId27" xr:uid="{EA668B17-66D9-4914-8CCA-6270540537CB}"/>
-    <hyperlink ref="G12" r:id="rId28" xr:uid="{A95E50CD-0F2B-42EB-A612-F26689DBB1BD}"/>
-    <hyperlink ref="G13" r:id="rId29" xr:uid="{A47CD37A-AB72-47AE-B101-3D17B982BBA4}"/>
-    <hyperlink ref="G14" r:id="rId30" xr:uid="{6157CC72-7B08-409E-9726-7860E43890F2}"/>
-    <hyperlink ref="G15" r:id="rId31" xr:uid="{5170F63F-E451-4F56-9E16-342D86EBC5EE}"/>
-    <hyperlink ref="G16" r:id="rId32" xr:uid="{68387AC1-0AFF-4B09-80A2-0E1265035880}"/>
-    <hyperlink ref="G17" r:id="rId33" xr:uid="{1245DC23-B5EB-4055-B446-16726C778FA2}"/>
-    <hyperlink ref="G18" r:id="rId34" xr:uid="{1217DDB9-52C2-422A-8A1B-09D810B1EDDC}"/>
-    <hyperlink ref="H2" r:id="rId35" xr:uid="{21C64DF6-7CFB-4622-B705-E45DE97F54C3}"/>
-    <hyperlink ref="H3" r:id="rId36" xr:uid="{7615D67B-8115-4CDE-9A36-971CAE6D188C}"/>
-    <hyperlink ref="H4" r:id="rId37" xr:uid="{EEB5BA5E-4DFB-4A7B-ACC9-0909D78EBD39}"/>
-    <hyperlink ref="H5" r:id="rId38" xr:uid="{54982B05-AFA0-41A0-A6D7-85F7EB5120B5}"/>
-    <hyperlink ref="H6" r:id="rId39" xr:uid="{66BE5829-BD1A-48C1-8D52-7602BFF727D3}"/>
-    <hyperlink ref="H7" r:id="rId40" xr:uid="{4E82A843-4CDE-4D45-A6D2-73A90631024D}"/>
-    <hyperlink ref="H8" r:id="rId41" xr:uid="{19E2D800-BA3B-46DF-8B4E-F87BDD487A70}"/>
-    <hyperlink ref="H9" r:id="rId42" xr:uid="{20F0E94E-7680-4E46-ADC6-EFCF6E46EE8E}"/>
-    <hyperlink ref="H10" r:id="rId43" xr:uid="{6F9496C0-8CA4-4CDF-9D84-31A1F640E963}"/>
-    <hyperlink ref="H11" r:id="rId44" xr:uid="{0B141640-F3A7-45E5-A1A0-A4AAB76098BD}"/>
-    <hyperlink ref="H12" r:id="rId45" xr:uid="{3D7CF0F8-FBA9-4294-969E-610715CC9C49}"/>
-    <hyperlink ref="H13" r:id="rId46" xr:uid="{83131CC0-2803-41BC-A556-0751DE525F11}"/>
-    <hyperlink ref="H14" r:id="rId47" xr:uid="{760BD45C-1B1D-4646-918B-A896989D84DE}"/>
-    <hyperlink ref="H15" r:id="rId48" xr:uid="{E7EC7AB1-459C-4F7D-B9D1-9E4B6E1CF277}"/>
-    <hyperlink ref="H16" r:id="rId49" xr:uid="{58C1C938-00FA-42E3-8713-B0675000BB1E}"/>
-    <hyperlink ref="H17" r:id="rId50" xr:uid="{26F47CA2-B6BE-4086-A44D-13B25B751F3C}"/>
-    <hyperlink ref="H18" r:id="rId51" xr:uid="{1BDEA6F5-86FC-4D8D-BDE5-335306D6C4AB}"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{519CECF9-06B6-4E70-862E-6CF7F786775B}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{C598BACE-CE8B-49FD-881F-AD2471656F65}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{35C0BA64-C19E-484B-972E-D4843344E2B5}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{02073409-00C2-4C51-83EC-97A07CDF9BAB}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{CEEC7E8B-5F64-4DDD-BB5E-8202CED76FE4}"/>
+    <hyperlink ref="G7" r:id="rId6" xr:uid="{58EB83B7-5748-4AFA-9A18-DC92D6A5C3A5}"/>
+    <hyperlink ref="G8" r:id="rId7" xr:uid="{63324E66-EECF-420A-939D-9FC410ECA74B}"/>
+    <hyperlink ref="G9" r:id="rId8" xr:uid="{54F3D8AB-A6FA-4E4F-86DB-421A97E77B63}"/>
+    <hyperlink ref="G19" r:id="rId9" xr:uid="{A3BA962D-F109-4E59-B8E9-240AF405D6C7}"/>
+    <hyperlink ref="G18" r:id="rId10" xr:uid="{0BFA9F3D-5219-4B8C-B846-B76FFD0BF1F0}"/>
+    <hyperlink ref="G17" r:id="rId11" xr:uid="{2B6DAD25-A022-47B4-97A4-D1F53A16C922}"/>
+    <hyperlink ref="G14" r:id="rId12" xr:uid="{E67D244A-F5D5-478D-A098-E4333EDFDF4B}"/>
+    <hyperlink ref="G13" r:id="rId13" xr:uid="{5705BC2E-3933-42BB-9D8D-A4561DE31E87}"/>
+    <hyperlink ref="G12" r:id="rId14" xr:uid="{09FEC92A-8E57-4745-B2B1-CB173FE342AF}"/>
+    <hyperlink ref="G11" r:id="rId15" xr:uid="{D85B8645-75F4-4DBE-96B6-5E264C73B64D}"/>
+    <hyperlink ref="G10" r:id="rId16" xr:uid="{B42BB367-E930-4F01-8984-E1B2FFC1315A}"/>
+    <hyperlink ref="H2" r:id="rId17" xr:uid="{AC63E67E-A0B3-4A54-B1EA-D69352B35E07}"/>
+    <hyperlink ref="H3" r:id="rId18" xr:uid="{28025270-E5D5-4156-B3FB-9CAB7029620E}"/>
+    <hyperlink ref="H4" r:id="rId19" xr:uid="{7BF3CEDE-E935-45C4-AB8D-C785568BAD81}"/>
+    <hyperlink ref="H5" r:id="rId20" xr:uid="{3ECF6EA4-A634-4F9B-B1AB-0A182259698F}"/>
+    <hyperlink ref="H6" r:id="rId21" xr:uid="{7412DBB7-8AF9-4525-B14C-686F7197DFE7}"/>
+    <hyperlink ref="H7" r:id="rId22" xr:uid="{F9D5EEB3-CFF4-4E31-B844-D1A3572D9FA9}"/>
+    <hyperlink ref="H8" r:id="rId23" xr:uid="{63C8E88F-8E99-4823-B700-9B5B55D315CF}"/>
+    <hyperlink ref="H9" r:id="rId24" xr:uid="{C8D10D9F-D84E-41EB-AA2A-0C871FD32342}"/>
+    <hyperlink ref="H10" r:id="rId25" xr:uid="{85687F6A-272F-45B5-8586-33E1B62F6EB3}"/>
+    <hyperlink ref="H11" r:id="rId26" xr:uid="{EA668B17-66D9-4914-8CCA-6270540537CB}"/>
+    <hyperlink ref="H12" r:id="rId27" xr:uid="{A95E50CD-0F2B-42EB-A612-F26689DBB1BD}"/>
+    <hyperlink ref="H13" r:id="rId28" xr:uid="{A47CD37A-AB72-47AE-B101-3D17B982BBA4}"/>
+    <hyperlink ref="H14" r:id="rId29" xr:uid="{6157CC72-7B08-409E-9726-7860E43890F2}"/>
+    <hyperlink ref="H17" r:id="rId30" xr:uid="{5170F63F-E451-4F56-9E16-342D86EBC5EE}"/>
+    <hyperlink ref="H18" r:id="rId31" xr:uid="{68387AC1-0AFF-4B09-80A2-0E1265035880}"/>
+    <hyperlink ref="H19" r:id="rId32" xr:uid="{1217DDB9-52C2-422A-8A1B-09D810B1EDDC}"/>
+    <hyperlink ref="I2" r:id="rId33" xr:uid="{21C64DF6-7CFB-4622-B705-E45DE97F54C3}"/>
+    <hyperlink ref="I3" r:id="rId34" xr:uid="{7615D67B-8115-4CDE-9A36-971CAE6D188C}"/>
+    <hyperlink ref="I4" r:id="rId35" xr:uid="{EEB5BA5E-4DFB-4A7B-ACC9-0909D78EBD39}"/>
+    <hyperlink ref="I5" r:id="rId36" xr:uid="{54982B05-AFA0-41A0-A6D7-85F7EB5120B5}"/>
+    <hyperlink ref="I6" r:id="rId37" xr:uid="{66BE5829-BD1A-48C1-8D52-7602BFF727D3}"/>
+    <hyperlink ref="I7" r:id="rId38" xr:uid="{4E82A843-4CDE-4D45-A6D2-73A90631024D}"/>
+    <hyperlink ref="I8" r:id="rId39" xr:uid="{19E2D800-BA3B-46DF-8B4E-F87BDD487A70}"/>
+    <hyperlink ref="I9" r:id="rId40" xr:uid="{20F0E94E-7680-4E46-ADC6-EFCF6E46EE8E}"/>
+    <hyperlink ref="I10" r:id="rId41" xr:uid="{6F9496C0-8CA4-4CDF-9D84-31A1F640E963}"/>
+    <hyperlink ref="I11" r:id="rId42" xr:uid="{0B141640-F3A7-45E5-A1A0-A4AAB76098BD}"/>
+    <hyperlink ref="I12" r:id="rId43" xr:uid="{3D7CF0F8-FBA9-4294-969E-610715CC9C49}"/>
+    <hyperlink ref="I13" r:id="rId44" xr:uid="{83131CC0-2803-41BC-A556-0751DE525F11}"/>
+    <hyperlink ref="I14" r:id="rId45" xr:uid="{760BD45C-1B1D-4646-918B-A896989D84DE}"/>
+    <hyperlink ref="I17" r:id="rId46" xr:uid="{E7EC7AB1-459C-4F7D-B9D1-9E4B6E1CF277}"/>
+    <hyperlink ref="I18" r:id="rId47" xr:uid="{58C1C938-00FA-42E3-8713-B0675000BB1E}"/>
+    <hyperlink ref="I19" r:id="rId48" xr:uid="{1BDEA6F5-86FC-4D8D-BDE5-335306D6C4AB}"/>
+    <hyperlink ref="J19" r:id="rId49" display="https://www.aliexpress.us/item/3256804056009500.html?spm=a2g0o.productlist.main.2.30276febieJcvn&amp;algo_pvid=909743e4-35c2-4e86-8d65-7d8d115ba05f&amp;algo_exp_id=909743e4-35c2-4e86-8d65-7d8d115ba05f-1&amp;pdp_ext_f=%7B%22order%22%3A%226336%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21USD%212.60%210.99%21%21%212.60%210.99%21%4021030a4b17757515549945973e60dd%2112000056072044332%21sea%21US%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3A1ebdde83%3Bm03_new_user%3A-29895%3BpisId%3A5000000197847434&amp;curPageLogUid=FLqHVcrTDnmC&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005004242324252%7C_p_origin_prod%3A" xr:uid="{F3A82335-6F0B-484A-A34D-65FC8405399D}"/>
+    <hyperlink ref="G15" r:id="rId50" xr:uid="{9491FBE4-3ECB-43E1-9F42-87AE38C4E241}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId52"/>
+  <pageSetup orientation="portrait" r:id="rId51"/>
   <tableParts count="1">
-    <tablePart r:id="rId53"/>
+    <tablePart r:id="rId52"/>
   </tableParts>
 </worksheet>
 </file>
--- a/System_development/Van-Hove/PCB_design/NMR Control Board v0.4.5/PCB_Control_Board_V_0.4.5_BoM.xlsx
+++ b/System_development/Van-Hove/PCB_design/NMR Control Board v0.4.5/PCB_Control_Board_V_0.4.5_BoM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jimmy\OneDrive\Documents\GitHub\Compact-NMR\System_development\Van-Hove\PCB_design\NMR Control Board v0.4.5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Compact-NMR\System_development\Van-Hove\PCB_design\NMR Control Board v0.4.5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38229ED6-EC72-499E-A2FA-0EFEC4653A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B951F328-7ACB-4DF4-9E6B-B351E56AC136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -454,45 +454,166 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="11">
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -508,19 +629,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{77BB0EBA-7ABD-4504-8B56-065735F83FAF}" name="Table1" displayName="Table1" ref="A1:J19" totalsRowShown="0" dataCellStyle="Hyperlink">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{77BB0EBA-7ABD-4504-8B56-065735F83FAF}" name="Table1" displayName="Table1" ref="A1:J19" totalsRowShown="0" dataDxfId="10" dataCellStyle="Hyperlink">
   <autoFilter ref="A1:J19" xr:uid="{77BB0EBA-7ABD-4504-8B56-065735F83FAF}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{125445A2-3E64-47DE-B26B-B36D09088CF3}" name="Designator" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{216FE132-2E18-40F7-A20A-BBFD26EC9D9D}" name="Reference"/>
-    <tableColumn id="2" xr3:uid="{978F1655-82E8-4669-A0DF-8FC026E7C5CF}" name="Component"/>
-    <tableColumn id="3" xr3:uid="{B31F8100-EC13-4F33-9A36-9A86A9F32309}" name="Amount"/>
-    <tableColumn id="4" xr3:uid="{B43A5C30-725D-41B9-ADE9-63C238F6193D}" name="Individual Cost" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{D2C286B4-CC55-46B0-8AA4-9B8C5B8E8252}" name="Total Cost" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{05D9E9D4-6FDB-4462-ABB6-67CC55FED516}" name="Vendor 1" dataDxfId="3" dataCellStyle="Hyperlink"/>
-    <tableColumn id="7" xr3:uid="{1351036D-0F08-4053-99CA-5A59FD8F86C2}" name="Vendor 2" dataDxfId="2" dataCellStyle="Hyperlink"/>
-    <tableColumn id="8" xr3:uid="{A6791673-9B53-4B1D-9E7C-56277BA3A1DB}" name="Vendor 3" dataDxfId="1" dataCellStyle="Hyperlink"/>
-    <tableColumn id="10" xr3:uid="{071AC535-6AD2-4958-86AD-B45E57B01236}" name="Vendor 4" dataDxfId="0" dataCellStyle="Hyperlink"/>
+    <tableColumn id="1" xr3:uid="{125445A2-3E64-47DE-B26B-B36D09088CF3}" name="Designator" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{216FE132-2E18-40F7-A20A-BBFD26EC9D9D}" name="Reference" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{978F1655-82E8-4669-A0DF-8FC026E7C5CF}" name="Component" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{B31F8100-EC13-4F33-9A36-9A86A9F32309}" name="Amount" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{B43A5C30-725D-41B9-ADE9-63C238F6193D}" name="Individual Cost" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{D2C286B4-CC55-46B0-8AA4-9B8C5B8E8252}" name="Total Cost" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{05D9E9D4-6FDB-4462-ABB6-67CC55FED516}" name="Vendor 1" dataDxfId="0" dataCellStyle="Hyperlink"/>
+    <tableColumn id="7" xr3:uid="{1351036D-0F08-4053-99CA-5A59FD8F86C2}" name="Vendor 2" dataDxfId="1" dataCellStyle="Hyperlink"/>
+    <tableColumn id="8" xr3:uid="{A6791673-9B53-4B1D-9E7C-56277BA3A1DB}" name="Vendor 3" dataDxfId="9" dataCellStyle="Hyperlink"/>
+    <tableColumn id="10" xr3:uid="{071AC535-6AD2-4958-86AD-B45E57B01236}" name="Vendor 4" dataDxfId="8" dataCellStyle="Hyperlink"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -844,20 +965,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="74" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="23.88671875" customWidth="1"/>
-    <col min="6" max="6" width="23.5546875" customWidth="1"/>
-    <col min="7" max="7" width="41.33203125" customWidth="1"/>
-    <col min="8" max="8" width="18.5546875" customWidth="1"/>
-    <col min="9" max="9" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="23.85546875" customWidth="1"/>
+    <col min="6" max="6" width="23.5703125" customWidth="1"/>
+    <col min="7" max="7" width="41.28515625" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -889,556 +1010,560 @@
         <v>105</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="6">
         <v>1</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="7">
         <v>0.52</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="7">
         <v>0.52</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="5"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="J2" s="4"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="6">
         <v>1</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="7">
         <v>0.77</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="7">
         <v>0.77</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="J3" s="5"/>
-    </row>
-    <row r="4" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="J3" s="4"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="6">
         <v>1</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="7">
         <v>1.25</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="7">
         <v>1.25</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="J4" s="5"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="J4" s="4"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="6">
         <v>1</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="7">
         <v>11.55</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="7">
         <v>11.55</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="J5" s="5"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="J5" s="4"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="6">
         <v>1</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="7">
         <v>10.8</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="7">
         <v>10.8</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="J6" s="5"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="J6" s="4"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="6">
         <v>1</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="7">
         <v>4.03</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="7">
         <v>4.03</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="J7" s="5"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="J7" s="4"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="6">
         <v>1</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="7">
         <v>0.61</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="7">
         <v>0.61</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="J8" s="5"/>
-    </row>
-    <row r="9" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="J8" s="4"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="6">
         <v>1</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="7">
         <v>0.25</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="7">
         <v>0.25</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="J9" s="5"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+      <c r="J9" s="4"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="6">
         <v>3</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="7">
         <v>0.13</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="7">
         <v>0.39</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="J10" s="5"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="6">
         <v>3</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="7">
         <v>0.11</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="7">
         <v>0.33</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="J11" s="5"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="6">
         <v>2</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="7">
         <v>0.19</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="7">
         <v>0.38</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="J12" s="5"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="6">
         <v>1</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="7">
         <v>0.18</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="7">
         <v>0.18</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="J13" s="5"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="6">
         <v>4</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="7">
         <v>0.19</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="7">
         <v>0.76</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="J14" s="5"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="6">
         <v>1</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="7">
         <v>0.1</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="7">
         <v>0.1</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="J15" s="5"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="6">
         <v>1</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="7">
         <v>0.1</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="7">
         <v>0.1</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="J16" s="5"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="6">
         <v>4</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="7">
         <v>0.1</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="7">
         <v>0.4</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I17" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="J17" s="5"/>
-    </row>
-    <row r="18" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="6">
         <v>3</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="7">
         <v>0.46</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="7">
         <v>1.38</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="I18" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="J18" s="5"/>
-    </row>
-    <row r="19" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="6">
         <v>12</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" s="7">
         <v>1.84</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19" s="7">
         <v>22.08</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="I19" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="J19" s="5" t="s">
+      <c r="J19" s="4" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E20" s="2" t="s">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E20" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="2">
         <f>SUM(F2:F19)</f>
         <v>55.88</v>
       </c>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
